--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/CodeSystem-jp-v3ActCode-famMeb-cs.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/CodeSystem-jp-v3ActCode-famMeb-cs.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Japanese supplement for HL7 v3 ActCode FAMMEB CodeSystem</t>
+    <t>JP Core FamilyMember CodeSystem</t>
   </si>
   <si>
     <t>Status</t>
